--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120102422</v>
+        <v>120103099</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>106190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,59 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100070</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441168</v>
+        <v>441148</v>
       </c>
       <c r="R2" t="n">
-        <v>6198861</v>
+        <v>6199058</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,17 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +781,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120102976</v>
+        <v>120104234</v>
       </c>
       <c r="B3" t="n">
-        <v>106190</v>
+        <v>102218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,35 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>225046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -865,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441198</v>
+        <v>441082</v>
       </c>
       <c r="R3" t="n">
-        <v>6198938</v>
+        <v>6198933</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,6 +889,11 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,7 +906,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120102939</v>
+        <v>120105542</v>
       </c>
       <c r="B4" t="n">
-        <v>105564</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -971,17 +962,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441085</v>
+        <v>441187</v>
       </c>
       <c r="R4" t="n">
-        <v>6198933</v>
+        <v>6198844</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,12 +1011,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,13 +1025,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105974</v>
+        <v>120103183</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>99566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,35 +1064,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222617</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441084</v>
+        <v>441109</v>
       </c>
       <c r="R5" t="n">
-        <v>6198915</v>
+        <v>6199104</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,12 +1134,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,12 +1148,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1181,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103183</v>
+        <v>120102422</v>
       </c>
       <c r="B6" t="n">
-        <v>99566</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,54 +1184,59 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222617</v>
+        <v>100070</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441109</v>
+        <v>441168</v>
       </c>
       <c r="R6" t="n">
-        <v>6199104</v>
+        <v>6198861</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1267,12 +1263,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1306,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105487</v>
+        <v>120105570</v>
       </c>
       <c r="B7" t="n">
-        <v>57405</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,25 +1318,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1344,11 +1345,7 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1361,13 +1358,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441144</v>
+        <v>441194</v>
       </c>
       <c r="R7" t="n">
-        <v>6199119</v>
+        <v>6198838</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,12 +1393,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,7 +1407,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1433,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105410</v>
+        <v>120102939</v>
       </c>
       <c r="B8" t="n">
-        <v>57489</v>
+        <v>105564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,25 +1437,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102623</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1471,13 +1463,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1485,13 +1481,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441089</v>
+        <v>441085</v>
       </c>
       <c r="R8" t="n">
-        <v>6198892</v>
+        <v>6198933</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1515,12 +1511,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,12 +1530,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103243</v>
+        <v>120105410</v>
       </c>
       <c r="B9" t="n">
-        <v>44687</v>
+        <v>57489</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,66 +1566,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100959</v>
+        <v>102623</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441208</v>
+        <v>441089</v>
       </c>
       <c r="R9" t="n">
-        <v>6198925</v>
+        <v>6198892</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,17 +1636,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,13 +1650,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1690,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120105570</v>
+        <v>120102976</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>106190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1706,35 +1689,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1742,13 +1729,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441194</v>
+        <v>441198</v>
       </c>
       <c r="R10" t="n">
-        <v>6198838</v>
+        <v>6198938</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1786,12 +1773,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1809,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120104234</v>
+        <v>120105904</v>
       </c>
       <c r="B11" t="n">
-        <v>102218</v>
+        <v>57329</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,39 +1809,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>225046</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1861,13 +1849,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441082</v>
+        <v>441089</v>
       </c>
       <c r="R11" t="n">
-        <v>6198933</v>
+        <v>6198892</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1891,17 +1879,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,13 +1893,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1934,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104226</v>
+        <v>120105974</v>
       </c>
       <c r="B12" t="n">
-        <v>102218</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,39 +1928,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225046</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1986,13 +1968,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441085</v>
+        <v>441084</v>
       </c>
       <c r="R12" t="n">
-        <v>6198931</v>
+        <v>6198915</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2016,17 +1998,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,13 +2012,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2059,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105542</v>
+        <v>120105396</v>
       </c>
       <c r="B13" t="n">
-        <v>57643</v>
+        <v>57489</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2071,20 +2047,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103008</v>
+        <v>102623</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2111,13 +2087,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441187</v>
+        <v>441206</v>
       </c>
       <c r="R13" t="n">
-        <v>6198844</v>
+        <v>6198969</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2146,12 +2122,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2165,7 +2136,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2183,10 +2154,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120105927</v>
+        <v>120104226</v>
       </c>
       <c r="B14" t="n">
-        <v>58013</v>
+        <v>102218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2195,39 +2166,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>225046</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2235,13 +2206,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441110</v>
+        <v>441085</v>
       </c>
       <c r="R14" t="n">
-        <v>6199010</v>
+        <v>6198931</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2265,12 +2236,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,12 +2255,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2302,10 +2279,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103176</v>
+        <v>120105927</v>
       </c>
       <c r="B15" t="n">
-        <v>99566</v>
+        <v>58013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,39 +2295,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222617</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2358,13 +2331,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441142</v>
+        <v>441110</v>
       </c>
       <c r="R15" t="n">
-        <v>6198980</v>
+        <v>6199010</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2388,12 +2361,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,13 +2375,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2426,10 +2398,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103099</v>
+        <v>120103243</v>
       </c>
       <c r="B16" t="n">
-        <v>106190</v>
+        <v>44687</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2438,54 +2410,63 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>100959</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441148</v>
+        <v>441208</v>
       </c>
       <c r="R16" t="n">
-        <v>6199058</v>
+        <v>6198925</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2512,12 +2493,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2532,7 +2518,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2550,10 +2536,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105396</v>
+        <v>120103176</v>
       </c>
       <c r="B17" t="n">
-        <v>57489</v>
+        <v>99566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,39 +2548,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102623</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2602,13 +2592,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441206</v>
+        <v>441142</v>
       </c>
       <c r="R17" t="n">
-        <v>6198969</v>
+        <v>6198980</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2632,12 +2622,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,12 +2636,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,10 +2660,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105904</v>
+        <v>120105487</v>
       </c>
       <c r="B18" t="n">
-        <v>57329</v>
+        <v>57405</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2685,16 +2676,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102977</v>
+        <v>102626</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2708,10 +2699,14 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2721,10 +2716,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441089</v>
+        <v>441144</v>
       </c>
       <c r="R18" t="n">
-        <v>6198892</v>
+        <v>6199119</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2751,12 +2746,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1673,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120102976</v>
+        <v>120105904</v>
       </c>
       <c r="B10" t="n">
-        <v>106190</v>
+        <v>57329</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,43 +1685,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1729,13 +1725,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441198</v>
+        <v>441089</v>
       </c>
       <c r="R10" t="n">
-        <v>6198938</v>
+        <v>6198892</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,12 +1755,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,13 +1769,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1797,10 +1792,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105904</v>
+        <v>120105974</v>
       </c>
       <c r="B11" t="n">
-        <v>57329</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,25 +1804,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1839,7 +1834,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1849,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441089</v>
+        <v>441084</v>
       </c>
       <c r="R11" t="n">
-        <v>6198892</v>
+        <v>6198915</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1879,12 +1874,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,7 +1893,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1916,10 +1911,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105974</v>
+        <v>120102976</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>106190</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,35 +1927,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1968,13 +1967,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441084</v>
+        <v>441198</v>
       </c>
       <c r="R12" t="n">
-        <v>6198915</v>
+        <v>6198938</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1998,12 +1997,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,12 +2011,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120103099</v>
+        <v>120103183</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>99566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>222617</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441148</v>
+        <v>441109</v>
       </c>
       <c r="R2" t="n">
-        <v>6199058</v>
+        <v>6199104</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120104234</v>
+        <v>120103176</v>
       </c>
       <c r="B3" t="n">
-        <v>102218</v>
+        <v>99566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,36 +811,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>225046</v>
+        <v>222617</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -851,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441082</v>
+        <v>441142</v>
       </c>
       <c r="R3" t="n">
-        <v>6198933</v>
+        <v>6198980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,17 +885,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +905,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105542</v>
+        <v>120102422</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>56266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,53 +935,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441187</v>
+        <v>441168</v>
       </c>
       <c r="R4" t="n">
-        <v>6198844</v>
+        <v>6198861</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,12 +1019,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,12 +1033,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120103183</v>
+        <v>120105542</v>
       </c>
       <c r="B5" t="n">
-        <v>99566</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,39 +1073,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222617</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441109</v>
+        <v>441187</v>
       </c>
       <c r="R5" t="n">
-        <v>6199104</v>
+        <v>6198844</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,12 +1139,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,13 +1158,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1172,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102422</v>
+        <v>120104234</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>102218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,27 +1193,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100070</v>
+        <v>225046</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1212,31 +1217,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441168</v>
+        <v>441082</v>
       </c>
       <c r="R6" t="n">
-        <v>6198861</v>
+        <v>6198933</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105570</v>
+        <v>120105396</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>57489</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,20 +1318,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441194</v>
+        <v>441206</v>
       </c>
       <c r="R7" t="n">
-        <v>6198838</v>
+        <v>6198969</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120102939</v>
+        <v>120105904</v>
       </c>
       <c r="B8" t="n">
-        <v>105564</v>
+        <v>57329</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,25 +1437,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1463,17 +1463,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1481,13 +1477,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441085</v>
+        <v>441089</v>
       </c>
       <c r="R8" t="n">
-        <v>6198933</v>
+        <v>6198892</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,17 +1507,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,13 +1521,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105410</v>
+        <v>120105570</v>
       </c>
       <c r="B9" t="n">
-        <v>57489</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,20 +1556,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1606,13 +1596,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441089</v>
+        <v>441194</v>
       </c>
       <c r="R9" t="n">
-        <v>6198892</v>
+        <v>6198838</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1636,12 +1626,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,7 +1645,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120105904</v>
+        <v>120105927</v>
       </c>
       <c r="B10" t="n">
-        <v>57329</v>
+        <v>58013</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,20 +1675,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1715,7 +1705,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1725,10 +1715,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441089</v>
+        <v>441110</v>
       </c>
       <c r="R10" t="n">
-        <v>6198892</v>
+        <v>6199010</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1774,7 +1764,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1792,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105974</v>
+        <v>120105410</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>57489</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,20 +1794,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1834,7 +1824,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1844,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441084</v>
+        <v>441089</v>
       </c>
       <c r="R11" t="n">
-        <v>6198915</v>
+        <v>6198892</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1874,12 +1864,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1883,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1911,10 +1901,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120102976</v>
+        <v>120103243</v>
       </c>
       <c r="B12" t="n">
-        <v>106190</v>
+        <v>44687</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,25 +1913,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>100959</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1951,26 +1941,35 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441198</v>
+        <v>441208</v>
       </c>
       <c r="R12" t="n">
-        <v>6198938</v>
+        <v>6198925</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2005,6 +2004,11 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2021,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2035,10 +2039,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105396</v>
+        <v>120105974</v>
       </c>
       <c r="B13" t="n">
-        <v>57489</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,20 +2051,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2077,7 +2081,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2087,10 +2091,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441206</v>
+        <v>441084</v>
       </c>
       <c r="R13" t="n">
-        <v>6198969</v>
+        <v>6198915</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2117,12 +2121,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,7 +2140,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2154,10 +2158,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104226</v>
+        <v>120102976</v>
       </c>
       <c r="B14" t="n">
-        <v>102218</v>
+        <v>106190</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,31 +2170,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225046</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2206,10 +2214,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441085</v>
+        <v>441198</v>
       </c>
       <c r="R14" t="n">
-        <v>6198931</v>
+        <v>6198938</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2244,11 +2252,6 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2261,7 +2264,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2279,10 +2282,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105927</v>
+        <v>120104226</v>
       </c>
       <c r="B15" t="n">
-        <v>58013</v>
+        <v>102218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,39 +2294,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>225046</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2331,13 +2334,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441110</v>
+        <v>441085</v>
       </c>
       <c r="R15" t="n">
-        <v>6199010</v>
+        <v>6198931</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2361,12 +2364,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,12 +2383,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2398,10 +2407,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103243</v>
+        <v>120105487</v>
       </c>
       <c r="B16" t="n">
-        <v>44687</v>
+        <v>57405</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2410,66 +2419,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100959</v>
+        <v>102626</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441208</v>
+        <v>441144</v>
       </c>
       <c r="R16" t="n">
-        <v>6198925</v>
+        <v>6199119</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2512,13 +2512,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103176</v>
+        <v>120102939</v>
       </c>
       <c r="B17" t="n">
-        <v>99566</v>
+        <v>105564</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,40 +2547,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222617</v>
+        <v>220785</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2592,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441142</v>
+        <v>441085</v>
       </c>
       <c r="R17" t="n">
-        <v>6198980</v>
+        <v>6198933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2622,12 +2621,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,7 +2646,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2660,10 +2664,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105487</v>
+        <v>120103099</v>
       </c>
       <c r="B18" t="n">
-        <v>57405</v>
+        <v>106190</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2672,43 +2676,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102626</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2716,13 +2720,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441144</v>
+        <v>441148</v>
       </c>
       <c r="R18" t="n">
-        <v>6199119</v>
+        <v>6199058</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2754,23 +2758,19 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1306,10 +1306,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105396</v>
+        <v>120105904</v>
       </c>
       <c r="B7" t="n">
-        <v>57489</v>
+        <v>57329</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441206</v>
+        <v>441089</v>
       </c>
       <c r="R7" t="n">
-        <v>6198969</v>
+        <v>6198892</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105904</v>
+        <v>120105396</v>
       </c>
       <c r="B8" t="n">
-        <v>57329</v>
+        <v>57489</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,21 +1441,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>102623</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441089</v>
+        <v>441206</v>
       </c>
       <c r="R8" t="n">
-        <v>6198892</v>
+        <v>6198969</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120103183</v>
+        <v>120103176</v>
       </c>
       <c r="B2" t="n">
         <v>99566</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441109</v>
+        <v>441142</v>
       </c>
       <c r="R2" t="n">
-        <v>6199104</v>
+        <v>6198980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120103176</v>
+        <v>120104234</v>
       </c>
       <c r="B3" t="n">
-        <v>99566</v>
+        <v>102218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,40 +811,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222617</v>
+        <v>225046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -855,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441142</v>
+        <v>441082</v>
       </c>
       <c r="R3" t="n">
-        <v>6198980</v>
+        <v>6198933</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,12 +881,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +906,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120102422</v>
+        <v>120102976</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
+        <v>106190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,59 +936,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100070</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441168</v>
+        <v>441198</v>
       </c>
       <c r="R4" t="n">
-        <v>6198861</v>
+        <v>6198938</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,11 +1018,6 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,7 +1030,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105542</v>
+        <v>120102939</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>105564</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,25 +1060,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1095,13 +1086,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441187</v>
+        <v>441085</v>
       </c>
       <c r="R5" t="n">
-        <v>6198844</v>
+        <v>6198933</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,12 +1139,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,12 +1153,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1181,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104234</v>
+        <v>120103243</v>
       </c>
       <c r="B6" t="n">
-        <v>102218</v>
+        <v>44687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,50 +1189,63 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225046</v>
+        <v>100959</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Euroleon nostras</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fourcroy, 1785)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441082</v>
+        <v>441208</v>
       </c>
       <c r="R6" t="n">
-        <v>6198933</v>
+        <v>6198925</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1273,7 +1282,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Levande ung alm</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1297,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1306,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105904</v>
+        <v>120105542</v>
       </c>
       <c r="B7" t="n">
-        <v>57329</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,25 +1327,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1348,7 +1357,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1358,13 +1367,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441089</v>
+        <v>441187</v>
       </c>
       <c r="R7" t="n">
-        <v>6198892</v>
+        <v>6198844</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,12 +1397,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,7 +1421,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105396</v>
+        <v>120103099</v>
       </c>
       <c r="B8" t="n">
-        <v>57489</v>
+        <v>106190</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,39 +1451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102623</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1477,13 +1495,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441206</v>
+        <v>441148</v>
       </c>
       <c r="R8" t="n">
-        <v>6198969</v>
+        <v>6199058</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,12 +1525,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,12 +1539,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1544,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105570</v>
+        <v>120105927</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>58013</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,21 +1579,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1586,7 +1605,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1596,13 +1615,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441194</v>
+        <v>441110</v>
       </c>
       <c r="R9" t="n">
-        <v>6198838</v>
+        <v>6199010</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1626,12 +1645,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,7 +1664,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1682,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120105927</v>
+        <v>120102422</v>
       </c>
       <c r="B10" t="n">
-        <v>58013</v>
+        <v>56266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,20 +1694,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>100070</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1699,29 +1718,38 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441110</v>
+        <v>441168</v>
       </c>
       <c r="R10" t="n">
-        <v>6199010</v>
+        <v>6198861</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1745,12 +1773,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,12 +1792,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1901,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120103243</v>
+        <v>120105487</v>
       </c>
       <c r="B12" t="n">
-        <v>44687</v>
+        <v>57405</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1913,66 +1947,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100959</v>
+        <v>102626</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441208</v>
+        <v>441144</v>
       </c>
       <c r="R12" t="n">
-        <v>6198925</v>
+        <v>6199119</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2001,12 +2026,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,13 +2040,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2039,7 +2063,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105974</v>
+        <v>120105570</v>
       </c>
       <c r="B13" t="n">
         <v>57326</v>
@@ -2081,7 +2105,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2091,13 +2115,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441084</v>
+        <v>441194</v>
       </c>
       <c r="R13" t="n">
-        <v>6198915</v>
+        <v>6198838</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,12 +2145,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,7 +2164,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2158,10 +2182,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120102976</v>
+        <v>120104226</v>
       </c>
       <c r="B14" t="n">
-        <v>106190</v>
+        <v>102218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,35 +2194,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>225046</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2214,10 +2234,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441198</v>
+        <v>441085</v>
       </c>
       <c r="R14" t="n">
-        <v>6198938</v>
+        <v>6198931</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2252,6 +2272,11 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2264,7 +2289,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2282,10 +2307,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104226</v>
+        <v>120105974</v>
       </c>
       <c r="B15" t="n">
-        <v>102218</v>
+        <v>57326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,39 +2319,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>225046</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2334,13 +2359,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441085</v>
+        <v>441084</v>
       </c>
       <c r="R15" t="n">
-        <v>6198931</v>
+        <v>6198915</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2364,17 +2389,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,13 +2403,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2407,10 +2426,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120105487</v>
+        <v>120105396</v>
       </c>
       <c r="B16" t="n">
-        <v>57405</v>
+        <v>57489</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2423,21 +2442,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2446,14 +2465,10 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2463,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441144</v>
+        <v>441206</v>
       </c>
       <c r="R16" t="n">
-        <v>6199119</v>
+        <v>6198969</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2498,12 +2513,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2535,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120102939</v>
+        <v>120103183</v>
       </c>
       <c r="B17" t="n">
-        <v>105564</v>
+        <v>99566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,40 +2557,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2591,10 +2601,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441085</v>
+        <v>441109</v>
       </c>
       <c r="R17" t="n">
-        <v>6198933</v>
+        <v>6199104</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2621,17 +2631,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,7 +2651,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2664,10 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120103099</v>
+        <v>120105904</v>
       </c>
       <c r="B18" t="n">
-        <v>106190</v>
+        <v>57329</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2676,43 +2681,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>102977</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2720,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441148</v>
+        <v>441089</v>
       </c>
       <c r="R18" t="n">
-        <v>6199058</v>
+        <v>6198892</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,13 +2765,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -2426,10 +2426,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120105396</v>
+        <v>120103183</v>
       </c>
       <c r="B16" t="n">
-        <v>57489</v>
+        <v>99566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2438,39 +2438,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102623</v>
+        <v>222617</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2478,13 +2482,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441206</v>
+        <v>441109</v>
       </c>
       <c r="R16" t="n">
-        <v>6198969</v>
+        <v>6199104</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2508,12 +2512,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,12 +2526,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103183</v>
+        <v>120105396</v>
       </c>
       <c r="B17" t="n">
-        <v>99566</v>
+        <v>57489</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,43 +2562,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222617</v>
+        <v>102623</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2601,13 +2602,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441109</v>
+        <v>441206</v>
       </c>
       <c r="R17" t="n">
-        <v>6199104</v>
+        <v>6198969</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2631,12 +2632,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,13 +2646,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103243</v>
+        <v>120105542</v>
       </c>
       <c r="B6" t="n">
-        <v>44687</v>
+        <v>57643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,66 +1189,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100959</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441208</v>
+        <v>441187</v>
       </c>
       <c r="R6" t="n">
-        <v>6198925</v>
+        <v>6198844</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,12 +1264,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,13 +1278,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1315,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105542</v>
+        <v>120103243</v>
       </c>
       <c r="B7" t="n">
-        <v>57643</v>
+        <v>44687</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,53 +1313,66 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>100959</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441187</v>
+        <v>441208</v>
       </c>
       <c r="R7" t="n">
-        <v>6198844</v>
+        <v>6198925</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,12 +1401,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,12 +1415,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120105542</v>
+        <v>120103243</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>44687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,53 +1189,66 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>100959</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441187</v>
+        <v>441208</v>
       </c>
       <c r="R6" t="n">
-        <v>6198844</v>
+        <v>6198925</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,12 +1277,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,12 +1291,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103243</v>
+        <v>120105542</v>
       </c>
       <c r="B7" t="n">
-        <v>44687</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,66 +1327,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100959</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441208</v>
+        <v>441187</v>
       </c>
       <c r="R7" t="n">
-        <v>6198925</v>
+        <v>6198844</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1401,12 +1402,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,13 +1416,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120103176</v>
+        <v>120105487</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
+        <v>57415</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222617</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441142</v>
+        <v>441144</v>
       </c>
       <c r="R2" t="n">
-        <v>6198980</v>
+        <v>6199119</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,13 +780,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +806,7 @@
         <v>120104234</v>
       </c>
       <c r="B3" t="n">
-        <v>102218</v>
+        <v>102241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120102976</v>
+        <v>120105410</v>
       </c>
       <c r="B4" t="n">
-        <v>106190</v>
+        <v>57499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,43 +940,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441198</v>
+        <v>441089</v>
       </c>
       <c r="R4" t="n">
-        <v>6198938</v>
+        <v>6198892</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,13 +1024,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120102939</v>
+        <v>120105396</v>
       </c>
       <c r="B5" t="n">
-        <v>105564</v>
+        <v>57499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1086,17 +1085,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441085</v>
+        <v>441206</v>
       </c>
       <c r="R5" t="n">
-        <v>6198933</v>
+        <v>6198969</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,24 +1137,18 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120105542</v>
+        <v>120103243</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>44696</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,53 +1178,66 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>100959</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441187</v>
+        <v>441208</v>
       </c>
       <c r="R6" t="n">
-        <v>6198844</v>
+        <v>6198925</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,12 +1266,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,12 +1280,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103243</v>
+        <v>120103176</v>
       </c>
       <c r="B7" t="n">
-        <v>44687</v>
+        <v>99589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,63 +1316,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100959</v>
+        <v>222617</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441208</v>
+        <v>441142</v>
       </c>
       <c r="R7" t="n">
-        <v>6198925</v>
+        <v>6198980</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1396,17 +1390,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1410,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120103099</v>
+        <v>120105974</v>
       </c>
       <c r="B8" t="n">
-        <v>106190</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1455,39 +1444,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1495,13 +1480,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441148</v>
+        <v>441084</v>
       </c>
       <c r="R8" t="n">
-        <v>6199058</v>
+        <v>6198915</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,12 +1510,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,13 +1524,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1563,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105927</v>
+        <v>120102422</v>
       </c>
       <c r="B9" t="n">
-        <v>58013</v>
+        <v>56276</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1575,20 +1559,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>100070</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1599,29 +1583,38 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441110</v>
+        <v>441168</v>
       </c>
       <c r="R9" t="n">
-        <v>6199010</v>
+        <v>6198861</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,12 +1638,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,12 +1657,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120102422</v>
+        <v>120102939</v>
       </c>
       <c r="B10" t="n">
-        <v>56266</v>
+        <v>105588</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,25 +1693,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100070</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1722,31 +1721,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441168</v>
+        <v>441085</v>
       </c>
       <c r="R10" t="n">
-        <v>6198861</v>
+        <v>6198933</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1783,7 +1777,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,7 +1792,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105410</v>
+        <v>120105904</v>
       </c>
       <c r="B11" t="n">
-        <v>57489</v>
+        <v>57339</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1832,21 +1826,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102623</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1858,7 +1852,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1898,12 +1892,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,7 +1911,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1935,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105487</v>
+        <v>120104226</v>
       </c>
       <c r="B12" t="n">
-        <v>57405</v>
+        <v>102241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1947,43 +1941,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102626</v>
+        <v>225046</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1991,13 +1981,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441144</v>
+        <v>441085</v>
       </c>
       <c r="R12" t="n">
-        <v>6199119</v>
+        <v>6198931</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2026,12 +2016,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,12 +2030,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2066,7 +2057,7 @@
         <v>120105570</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2182,10 +2173,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104226</v>
+        <v>120103183</v>
       </c>
       <c r="B14" t="n">
-        <v>102218</v>
+        <v>99589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2194,36 +2185,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225046</v>
+        <v>222617</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2234,10 +2229,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441085</v>
+        <v>441109</v>
       </c>
       <c r="R14" t="n">
-        <v>6198931</v>
+        <v>6199104</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2264,17 +2259,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2289,7 +2279,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2307,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105974</v>
+        <v>120105542</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>57653</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2323,16 +2313,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2349,7 +2339,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2359,13 +2349,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441084</v>
+        <v>441187</v>
       </c>
       <c r="R15" t="n">
-        <v>6198915</v>
+        <v>6198844</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2389,12 +2379,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,7 +2403,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2426,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103183</v>
+        <v>120102976</v>
       </c>
       <c r="B16" t="n">
-        <v>99566</v>
+        <v>106214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2442,36 +2437,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441109</v>
+        <v>441198</v>
       </c>
       <c r="R16" t="n">
-        <v>6199104</v>
+        <v>6198938</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2512,12 +2507,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2532,7 +2527,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2550,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105396</v>
+        <v>120105927</v>
       </c>
       <c r="B17" t="n">
-        <v>57489</v>
+        <v>58023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,25 +2557,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102623</v>
+        <v>103055</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441206</v>
+        <v>441110</v>
       </c>
       <c r="R17" t="n">
-        <v>6198969</v>
+        <v>6199010</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2632,12 +2627,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,10 +2664,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105904</v>
+        <v>120103099</v>
       </c>
       <c r="B18" t="n">
-        <v>57329</v>
+        <v>106214</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2681,39 +2676,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102977</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2721,13 +2720,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441089</v>
+        <v>441148</v>
       </c>
       <c r="R18" t="n">
-        <v>6198892</v>
+        <v>6199058</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2765,12 +2764,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1810,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105904</v>
+        <v>120104226</v>
       </c>
       <c r="B11" t="n">
-        <v>57339</v>
+        <v>102241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,39 +1822,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>225046</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441089</v>
+        <v>441085</v>
       </c>
       <c r="R11" t="n">
-        <v>6198892</v>
+        <v>6198931</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1892,12 +1892,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,12 +1911,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1929,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104226</v>
+        <v>120105904</v>
       </c>
       <c r="B12" t="n">
-        <v>102241</v>
+        <v>57339</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,39 +1947,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225046</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1981,13 +1987,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441085</v>
+        <v>441089</v>
       </c>
       <c r="R12" t="n">
-        <v>6198931</v>
+        <v>6198892</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2011,17 +2017,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2030,13 +2031,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105487</v>
+        <v>120102422</v>
       </c>
       <c r="B2" t="n">
-        <v>57415</v>
+        <v>56276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102626</v>
+        <v>100070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,31 +713,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441144</v>
+        <v>441168</v>
       </c>
       <c r="R2" t="n">
-        <v>6199119</v>
+        <v>6198861</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,12 +771,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +785,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120104234</v>
+        <v>120105487</v>
       </c>
       <c r="B3" t="n">
-        <v>102241</v>
+        <v>57415</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,39 +821,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>225046</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441082</v>
+        <v>441144</v>
       </c>
       <c r="R3" t="n">
-        <v>6198933</v>
+        <v>6199119</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,12 +900,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Levande ung alm</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,13 +914,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105410</v>
+        <v>120105396</v>
       </c>
       <c r="B4" t="n">
         <v>57499</v>
@@ -970,7 +979,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -980,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441089</v>
+        <v>441206</v>
       </c>
       <c r="R4" t="n">
-        <v>6198892</v>
+        <v>6198969</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,12 +1019,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105396</v>
+        <v>120102976</v>
       </c>
       <c r="B5" t="n">
-        <v>57499</v>
+        <v>106214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,39 +1068,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102623</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1099,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441206</v>
+        <v>441198</v>
       </c>
       <c r="R5" t="n">
-        <v>6198969</v>
+        <v>6198938</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,12 +1156,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103243</v>
+        <v>120103176</v>
       </c>
       <c r="B6" t="n">
-        <v>44696</v>
+        <v>99589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,63 +1192,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100959</v>
+        <v>222617</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441208</v>
+        <v>441142</v>
       </c>
       <c r="R6" t="n">
-        <v>6198925</v>
+        <v>6198980</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1261,17 +1266,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103176</v>
+        <v>120105410</v>
       </c>
       <c r="B7" t="n">
-        <v>99589</v>
+        <v>57499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,43 +1316,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222617</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1360,13 +1356,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441142</v>
+        <v>441089</v>
       </c>
       <c r="R7" t="n">
-        <v>6198980</v>
+        <v>6198892</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,13 +1400,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1428,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105974</v>
+        <v>120105542</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57653</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,16 +1439,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1465,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1480,13 +1475,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441084</v>
+        <v>441187</v>
       </c>
       <c r="R8" t="n">
-        <v>6198915</v>
+        <v>6198844</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,12 +1505,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120102422</v>
+        <v>120105904</v>
       </c>
       <c r="B9" t="n">
-        <v>56276</v>
+        <v>57339</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,20 +1559,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100070</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1583,38 +1583,29 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441168</v>
+        <v>441089</v>
       </c>
       <c r="R9" t="n">
-        <v>6198861</v>
+        <v>6198892</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1638,17 +1629,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,13 +1643,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1681,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120102939</v>
+        <v>120104234</v>
       </c>
       <c r="B10" t="n">
-        <v>105588</v>
+        <v>102241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,27 +1678,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1737,7 +1718,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441085</v>
+        <v>441082</v>
       </c>
       <c r="R10" t="n">
         <v>6198933</v>
@@ -1777,7 +1758,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,7 +1773,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120104226</v>
+        <v>120103243</v>
       </c>
       <c r="B11" t="n">
-        <v>102241</v>
+        <v>44696</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,50 +1803,63 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>225046</v>
+        <v>100959</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Euroleon nostras</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fourcroy, 1785)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441085</v>
+        <v>441208</v>
       </c>
       <c r="R11" t="n">
-        <v>6198931</v>
+        <v>6198925</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1902,7 +1896,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande ung alm</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,7 +1911,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1935,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105904</v>
+        <v>120105927</v>
       </c>
       <c r="B12" t="n">
-        <v>57339</v>
+        <v>58023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1947,20 +1941,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1977,7 +1971,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1987,10 +1981,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441089</v>
+        <v>441110</v>
       </c>
       <c r="R12" t="n">
-        <v>6198892</v>
+        <v>6199010</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2030,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2054,7 +2048,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105570</v>
+        <v>120105974</v>
       </c>
       <c r="B13" t="n">
         <v>57336</v>
@@ -2096,7 +2090,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,13 +2100,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441194</v>
+        <v>441084</v>
       </c>
       <c r="R13" t="n">
-        <v>6198838</v>
+        <v>6198915</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2136,12 +2130,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2149,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2173,10 +2167,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120103183</v>
+        <v>120103099</v>
       </c>
       <c r="B14" t="n">
-        <v>99589</v>
+        <v>106214</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2189,36 +2183,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2229,10 +2223,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441109</v>
+        <v>441148</v>
       </c>
       <c r="R14" t="n">
-        <v>6199104</v>
+        <v>6199058</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2259,12 +2253,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,7 +2273,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2297,10 +2291,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105542</v>
+        <v>120104226</v>
       </c>
       <c r="B15" t="n">
-        <v>57653</v>
+        <v>102241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,39 +2303,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103008</v>
+        <v>225046</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2349,13 +2343,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441187</v>
+        <v>441085</v>
       </c>
       <c r="R15" t="n">
-        <v>6198844</v>
+        <v>6198931</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,12 +2378,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,12 +2392,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2421,10 +2416,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102976</v>
+        <v>120102939</v>
       </c>
       <c r="B16" t="n">
-        <v>106214</v>
+        <v>105588</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,20 +2428,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2456,12 +2451,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2477,10 +2472,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441198</v>
+        <v>441085</v>
       </c>
       <c r="R16" t="n">
-        <v>6198938</v>
+        <v>6198933</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2515,6 +2510,11 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105927</v>
+        <v>120103183</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>99589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,35 +2561,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103055</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2597,13 +2601,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441110</v>
+        <v>441109</v>
       </c>
       <c r="R17" t="n">
-        <v>6199010</v>
+        <v>6199104</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2627,12 +2631,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2641,12 +2645,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2664,10 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120103099</v>
+        <v>120105570</v>
       </c>
       <c r="B18" t="n">
-        <v>106214</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,39 +2685,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2720,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441148</v>
+        <v>441194</v>
       </c>
       <c r="R18" t="n">
-        <v>6199058</v>
+        <v>6198838</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,12 +2751,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,13 +2765,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105410</v>
+        <v>120105542</v>
       </c>
       <c r="B7" t="n">
-        <v>57499</v>
+        <v>57653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441089</v>
+        <v>441187</v>
       </c>
       <c r="R7" t="n">
-        <v>6198892</v>
+        <v>6198844</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,12 +1386,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1410,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1423,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105542</v>
+        <v>120105410</v>
       </c>
       <c r="B8" t="n">
-        <v>57653</v>
+        <v>57499</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>102623</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1465,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1475,13 +1480,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441187</v>
+        <v>441089</v>
       </c>
       <c r="R8" t="n">
-        <v>6198844</v>
+        <v>6198892</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,7 +1510,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1513,11 +1518,6 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120102422</v>
+        <v>120102976</v>
       </c>
       <c r="B2" t="n">
-        <v>56276</v>
+        <v>106214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,59 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100070</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441168</v>
+        <v>441198</v>
       </c>
       <c r="R2" t="n">
-        <v>6198861</v>
+        <v>6198938</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,11 +769,6 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -791,7 +781,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105487</v>
+        <v>120103176</v>
       </c>
       <c r="B3" t="n">
-        <v>57415</v>
+        <v>99589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,43 +811,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>222617</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441144</v>
+        <v>441142</v>
       </c>
       <c r="R3" t="n">
-        <v>6199119</v>
+        <v>6198980</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,17 +885,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,12 +899,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105396</v>
+        <v>120103243</v>
       </c>
       <c r="B4" t="n">
-        <v>57499</v>
+        <v>44696</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,53 +935,66 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>100959</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441206</v>
+        <v>441208</v>
       </c>
       <c r="R4" t="n">
-        <v>6198969</v>
+        <v>6198925</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,18 +1026,24 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120102976</v>
+        <v>120103099</v>
       </c>
       <c r="B5" t="n">
         <v>106214</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441198</v>
+        <v>441148</v>
       </c>
       <c r="R5" t="n">
-        <v>6198938</v>
+        <v>6199058</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1142,12 +1147,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1167,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1180,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103176</v>
+        <v>120102939</v>
       </c>
       <c r="B6" t="n">
-        <v>99589</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,40 +1197,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222617</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1236,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441142</v>
+        <v>441085</v>
       </c>
       <c r="R6" t="n">
-        <v>6198980</v>
+        <v>6198933</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,12 +1271,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,7 +1296,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,10 +1314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105542</v>
+        <v>120105487</v>
       </c>
       <c r="B7" t="n">
-        <v>57653</v>
+        <v>57415</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,25 +1326,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,10 +1353,14 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1356,13 +1370,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441187</v>
+        <v>441144</v>
       </c>
       <c r="R7" t="n">
-        <v>6198844</v>
+        <v>6199119</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1405,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1410,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1547,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105904</v>
+        <v>120103183</v>
       </c>
       <c r="B9" t="n">
-        <v>57339</v>
+        <v>99589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,39 +1573,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>222617</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1599,13 +1617,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441089</v>
+        <v>441109</v>
       </c>
       <c r="R9" t="n">
-        <v>6198892</v>
+        <v>6199104</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,12 +1647,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,12 +1661,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1791,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103243</v>
+        <v>120102422</v>
       </c>
       <c r="B11" t="n">
-        <v>44696</v>
+        <v>56276</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,26 +1826,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100959</v>
+        <v>100070</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1834,15 +1853,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1856,10 +1871,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441208</v>
+        <v>441168</v>
       </c>
       <c r="R11" t="n">
-        <v>6198925</v>
+        <v>6198861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1896,7 +1911,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,7 +1926,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1929,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105927</v>
+        <v>120105974</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1945,21 +1960,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1971,7 +1986,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1981,10 +1996,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441110</v>
+        <v>441084</v>
       </c>
       <c r="R12" t="n">
-        <v>6199010</v>
+        <v>6198915</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2011,12 +2026,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2030,7 +2045,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2048,10 +2063,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105974</v>
+        <v>120104226</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>102241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2060,39 +2075,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>225046</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2100,13 +2115,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441084</v>
+        <v>441085</v>
       </c>
       <c r="R13" t="n">
-        <v>6198915</v>
+        <v>6198931</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,12 +2145,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,12 +2164,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2167,10 +2188,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120103099</v>
+        <v>120105570</v>
       </c>
       <c r="B14" t="n">
-        <v>106214</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2183,39 +2204,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2223,13 +2240,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441148</v>
+        <v>441194</v>
       </c>
       <c r="R14" t="n">
-        <v>6199058</v>
+        <v>6198838</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2253,12 +2270,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,13 +2284,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2291,10 +2307,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104226</v>
+        <v>120105396</v>
       </c>
       <c r="B15" t="n">
-        <v>102241</v>
+        <v>57499</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2303,39 +2319,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>225046</v>
+        <v>102623</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2343,13 +2359,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441085</v>
+        <v>441206</v>
       </c>
       <c r="R15" t="n">
-        <v>6198931</v>
+        <v>6198969</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2381,24 +2397,18 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2416,10 +2426,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102939</v>
+        <v>120105904</v>
       </c>
       <c r="B16" t="n">
-        <v>105588</v>
+        <v>57339</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2428,25 +2438,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2454,17 +2464,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2472,13 +2478,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441085</v>
+        <v>441089</v>
       </c>
       <c r="R16" t="n">
-        <v>6198933</v>
+        <v>6198892</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2502,17 +2508,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,13 +2522,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103183</v>
+        <v>120105542</v>
       </c>
       <c r="B17" t="n">
-        <v>99589</v>
+        <v>57653</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,39 +2561,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222617</v>
+        <v>103008</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2601,13 +2597,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441109</v>
+        <v>441187</v>
       </c>
       <c r="R17" t="n">
-        <v>6199104</v>
+        <v>6198844</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2631,12 +2627,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,13 +2646,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105570</v>
+        <v>120105927</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>58023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2711,7 +2711,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441194</v>
+        <v>441110</v>
       </c>
       <c r="R18" t="n">
-        <v>6198838</v>
+        <v>6199010</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -2545,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105542</v>
+        <v>120105927</v>
       </c>
       <c r="B17" t="n">
-        <v>57653</v>
+        <v>58023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441187</v>
+        <v>441110</v>
       </c>
       <c r="R17" t="n">
-        <v>6198844</v>
+        <v>6199010</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2627,17 +2627,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2651,7 +2646,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,10 +2664,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105927</v>
+        <v>120105542</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>57653</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2685,21 +2680,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2721,13 +2716,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441110</v>
+        <v>441187</v>
       </c>
       <c r="R18" t="n">
-        <v>6199010</v>
+        <v>6198844</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2751,12 +2746,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120102976</v>
+        <v>120103176</v>
       </c>
       <c r="B2" t="n">
-        <v>106214</v>
+        <v>99589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>222617</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441198</v>
+        <v>441142</v>
       </c>
       <c r="R2" t="n">
-        <v>6198938</v>
+        <v>6198980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120103176</v>
+        <v>120103099</v>
       </c>
       <c r="B3" t="n">
-        <v>99589</v>
+        <v>106214</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,36 +815,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441142</v>
+        <v>441148</v>
       </c>
       <c r="R3" t="n">
-        <v>6198980</v>
+        <v>6199058</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,12 +885,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120103243</v>
+        <v>120105487</v>
       </c>
       <c r="B4" t="n">
-        <v>44696</v>
+        <v>57415</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,66 +935,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100959</v>
+        <v>102626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441208</v>
+        <v>441144</v>
       </c>
       <c r="R4" t="n">
-        <v>6198925</v>
+        <v>6199119</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,12 +1014,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,13 +1028,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120103099</v>
+        <v>120103243</v>
       </c>
       <c r="B5" t="n">
-        <v>106214</v>
+        <v>44696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,54 +1063,63 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>100959</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441148</v>
+        <v>441208</v>
       </c>
       <c r="R5" t="n">
-        <v>6199058</v>
+        <v>6198925</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1147,12 +1146,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1171,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102939</v>
+        <v>120102422</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>56276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100070</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1225,26 +1229,31 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441085</v>
+        <v>441168</v>
       </c>
       <c r="R6" t="n">
-        <v>6198933</v>
+        <v>6198861</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,7 +1290,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,7 +1305,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1314,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105487</v>
+        <v>120105410</v>
       </c>
       <c r="B7" t="n">
-        <v>57415</v>
+        <v>57499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,21 +1339,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1353,11 +1362,7 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441144</v>
+        <v>441089</v>
       </c>
       <c r="R7" t="n">
-        <v>6199119</v>
+        <v>6198892</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1400,17 +1405,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105410</v>
+        <v>120105570</v>
       </c>
       <c r="B8" t="n">
-        <v>57499</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1454,20 +1454,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441089</v>
+        <v>441194</v>
       </c>
       <c r="R8" t="n">
-        <v>6198892</v>
+        <v>6198838</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103183</v>
+        <v>120105542</v>
       </c>
       <c r="B9" t="n">
-        <v>99589</v>
+        <v>57653</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1577,39 +1577,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222617</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1617,13 +1613,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441109</v>
+        <v>441187</v>
       </c>
       <c r="R9" t="n">
-        <v>6199104</v>
+        <v>6198844</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,12 +1643,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,13 +1662,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104234</v>
+        <v>120105974</v>
       </c>
       <c r="B10" t="n">
-        <v>102241</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1697,39 +1697,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225046</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441082</v>
+        <v>441084</v>
       </c>
       <c r="R10" t="n">
-        <v>6198933</v>
+        <v>6198915</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,17 +1767,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,13 +1781,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,10 +1804,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120102422</v>
+        <v>120103183</v>
       </c>
       <c r="B11" t="n">
-        <v>56276</v>
+        <v>99589</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,59 +1816,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100070</v>
+        <v>222617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441168</v>
+        <v>441109</v>
       </c>
       <c r="R11" t="n">
-        <v>6198861</v>
+        <v>6199104</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1901,17 +1890,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1926,7 +1910,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1944,10 +1928,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105974</v>
+        <v>120104234</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>102241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1956,39 +1940,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>225046</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1996,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441084</v>
+        <v>441082</v>
       </c>
       <c r="R12" t="n">
-        <v>6198915</v>
+        <v>6198933</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2026,12 +2010,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,12 +2029,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2188,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120105570</v>
+        <v>120105396</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2200,20 +2190,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2230,7 +2220,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2240,13 +2230,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441194</v>
+        <v>441206</v>
       </c>
       <c r="R14" t="n">
-        <v>6198838</v>
+        <v>6198969</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2289,7 +2279,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2307,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105396</v>
+        <v>120105927</v>
       </c>
       <c r="B15" t="n">
-        <v>57499</v>
+        <v>58023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,25 +2309,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102623</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2359,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441206</v>
+        <v>441110</v>
       </c>
       <c r="R15" t="n">
-        <v>6198969</v>
+        <v>6199010</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2389,12 +2379,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,10 +2416,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120105904</v>
+        <v>120102939</v>
       </c>
       <c r="B16" t="n">
-        <v>57339</v>
+        <v>105588</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2438,25 +2428,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2464,13 +2454,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2478,13 +2472,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441089</v>
+        <v>441085</v>
       </c>
       <c r="R16" t="n">
-        <v>6198892</v>
+        <v>6198933</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2508,12 +2502,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,12 +2521,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105927</v>
+        <v>120105904</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>57339</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2587,7 +2587,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441110</v>
+        <v>441089</v>
       </c>
       <c r="R17" t="n">
-        <v>6199010</v>
+        <v>6198892</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105542</v>
+        <v>120102976</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>106214</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,35 +2680,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103008</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2716,13 +2720,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441187</v>
+        <v>441198</v>
       </c>
       <c r="R18" t="n">
-        <v>6198844</v>
+        <v>6198938</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2751,12 +2755,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2765,12 +2764,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120103176</v>
+        <v>120105542</v>
       </c>
       <c r="B2" t="n">
-        <v>99589</v>
+        <v>57653</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222617</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441142</v>
+        <v>441187</v>
       </c>
       <c r="R2" t="n">
-        <v>6198980</v>
+        <v>6198844</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,13 +776,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120103099</v>
+        <v>120105904</v>
       </c>
       <c r="B3" t="n">
-        <v>106214</v>
+        <v>57339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,43 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441148</v>
+        <v>441089</v>
       </c>
       <c r="R3" t="n">
-        <v>6199058</v>
+        <v>6198892</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,13 +895,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105487</v>
+        <v>120105570</v>
       </c>
       <c r="B4" t="n">
-        <v>57415</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,11 +957,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -979,13 +970,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441144</v>
+        <v>441194</v>
       </c>
       <c r="R4" t="n">
-        <v>6199119</v>
+        <v>6198838</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,12 +1005,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1019,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120103243</v>
+        <v>120105927</v>
       </c>
       <c r="B5" t="n">
-        <v>44696</v>
+        <v>58023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,66 +1049,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100959</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441208</v>
+        <v>441110</v>
       </c>
       <c r="R5" t="n">
-        <v>6198925</v>
+        <v>6199010</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,17 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,13 +1133,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1323,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120105410</v>
+        <v>120102939</v>
       </c>
       <c r="B7" t="n">
-        <v>57499</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,25 +1302,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1361,13 +1328,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1375,13 +1346,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441089</v>
+        <v>441085</v>
       </c>
       <c r="R7" t="n">
-        <v>6198892</v>
+        <v>6198933</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1405,12 +1376,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,12 +1395,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105570</v>
+        <v>120102976</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>106214</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,35 +1435,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1494,13 +1475,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441194</v>
+        <v>441198</v>
       </c>
       <c r="R8" t="n">
-        <v>6198838</v>
+        <v>6198938</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1538,12 +1519,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1561,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105542</v>
+        <v>120105487</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>57415</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,25 +1555,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>102626</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1600,10 +1582,14 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1613,13 +1599,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441187</v>
+        <v>441144</v>
       </c>
       <c r="R9" t="n">
-        <v>6198844</v>
+        <v>6199119</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,7 +1634,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1667,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1685,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120105974</v>
+        <v>120104226</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>102241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1697,39 +1683,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>225046</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1737,13 +1723,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441084</v>
+        <v>441085</v>
       </c>
       <c r="R10" t="n">
-        <v>6198915</v>
+        <v>6198931</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,12 +1753,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,12 +1772,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1804,10 +1796,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103183</v>
+        <v>120105974</v>
       </c>
       <c r="B11" t="n">
-        <v>99589</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1820,39 +1812,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222617</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1860,13 +1848,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441109</v>
+        <v>441084</v>
       </c>
       <c r="R11" t="n">
-        <v>6199104</v>
+        <v>6198915</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,12 +1878,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,13 +1892,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1928,10 +1915,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104234</v>
+        <v>120105396</v>
       </c>
       <c r="B12" t="n">
-        <v>102241</v>
+        <v>57499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,39 +1927,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225046</v>
+        <v>102623</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1980,13 +1967,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441082</v>
+        <v>441206</v>
       </c>
       <c r="R12" t="n">
-        <v>6198933</v>
+        <v>6198969</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2018,24 +2005,18 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2053,10 +2034,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104226</v>
+        <v>120105410</v>
       </c>
       <c r="B13" t="n">
-        <v>102241</v>
+        <v>57499</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2065,39 +2046,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225046</v>
+        <v>102623</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2105,13 +2086,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441085</v>
+        <v>441089</v>
       </c>
       <c r="R13" t="n">
-        <v>6198931</v>
+        <v>6198892</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,17 +2116,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2154,13 +2130,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2178,10 +2153,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120105396</v>
+        <v>120104234</v>
       </c>
       <c r="B14" t="n">
-        <v>57499</v>
+        <v>102241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2190,39 +2165,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102623</v>
+        <v>225046</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2230,13 +2205,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441206</v>
+        <v>441082</v>
       </c>
       <c r="R14" t="n">
-        <v>6198969</v>
+        <v>6198933</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2268,18 +2243,24 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2297,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105927</v>
+        <v>120103176</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>99589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2313,35 +2294,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>222617</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2349,13 +2334,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441110</v>
+        <v>441142</v>
       </c>
       <c r="R15" t="n">
-        <v>6199010</v>
+        <v>6198980</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2379,12 +2364,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2393,12 +2378,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2416,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102939</v>
+        <v>120103183</v>
       </c>
       <c r="B16" t="n">
-        <v>105588</v>
+        <v>99589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2428,40 +2414,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>222617</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2472,10 +2458,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441085</v>
+        <v>441109</v>
       </c>
       <c r="R16" t="n">
-        <v>6198933</v>
+        <v>6199104</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2502,17 +2488,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2527,7 +2508,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2526,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105904</v>
+        <v>120103243</v>
       </c>
       <c r="B17" t="n">
-        <v>57339</v>
+        <v>44696</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,53 +2538,66 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>100959</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441089</v>
+        <v>441208</v>
       </c>
       <c r="R17" t="n">
-        <v>6198892</v>
+        <v>6198925</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2627,12 +2621,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2641,12 +2640,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120102976</v>
+        <v>120103099</v>
       </c>
       <c r="B18" t="n">
         <v>106214</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441198</v>
+        <v>441148</v>
       </c>
       <c r="R18" t="n">
-        <v>6198938</v>
+        <v>6199058</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105904</v>
+        <v>120105570</v>
       </c>
       <c r="B3" t="n">
-        <v>57339</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441089</v>
+        <v>441194</v>
       </c>
       <c r="R3" t="n">
-        <v>6198892</v>
+        <v>6198838</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,12 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105570</v>
+        <v>120105904</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>57339</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,7 +960,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441194</v>
+        <v>441089</v>
       </c>
       <c r="R4" t="n">
-        <v>6198838</v>
+        <v>6198892</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102422</v>
+        <v>120102939</v>
       </c>
       <c r="B6" t="n">
-        <v>56276</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100070</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1196,31 +1196,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441168</v>
+        <v>441085</v>
       </c>
       <c r="R6" t="n">
-        <v>6198861</v>
+        <v>6198933</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,7 +1252,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1267,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102939</v>
+        <v>120102422</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>100070</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1330,26 +1325,31 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441085</v>
+        <v>441168</v>
       </c>
       <c r="R7" t="n">
-        <v>6198933</v>
+        <v>6198861</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105542</v>
+        <v>120105904</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57339</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441187</v>
+        <v>441089</v>
       </c>
       <c r="R2" t="n">
-        <v>6198844</v>
+        <v>6198892</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105570</v>
+        <v>120102422</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +806,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441194</v>
+        <v>441168</v>
       </c>
       <c r="R3" t="n">
-        <v>6198838</v>
+        <v>6198861</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,18 +893,24 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105904</v>
+        <v>120104226</v>
       </c>
       <c r="B4" t="n">
-        <v>57339</v>
+        <v>102241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +940,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>225046</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,13 +980,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441089</v>
+        <v>441085</v>
       </c>
       <c r="R4" t="n">
-        <v>6198892</v>
+        <v>6198931</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,12 +1010,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +1029,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105927</v>
+        <v>120102976</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>106214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,35 +1069,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1089,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441110</v>
+        <v>441198</v>
       </c>
       <c r="R5" t="n">
-        <v>6199010</v>
+        <v>6198938</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,12 +1139,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,12 +1153,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1156,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102939</v>
+        <v>120103099</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>106214</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1189,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,17 +1212,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1212,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441085</v>
+        <v>441148</v>
       </c>
       <c r="R6" t="n">
-        <v>6198933</v>
+        <v>6199058</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,17 +1263,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En levande ung stam.</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1283,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102422</v>
+        <v>120102939</v>
       </c>
       <c r="B7" t="n">
-        <v>56276</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100070</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,31 +1341,26 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441168</v>
+        <v>441085</v>
       </c>
       <c r="R7" t="n">
-        <v>6198861</v>
+        <v>6198933</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1386,7 +1397,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>En levande ung stam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1412,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1419,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120102976</v>
+        <v>120105487</v>
       </c>
       <c r="B8" t="n">
-        <v>106214</v>
+        <v>57415</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,43 +1442,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>102626</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1475,13 +1486,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441198</v>
+        <v>441144</v>
       </c>
       <c r="R8" t="n">
-        <v>6198938</v>
+        <v>6199119</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,7 +1521,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,13 +1535,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,10 +1558,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105487</v>
+        <v>120105542</v>
       </c>
       <c r="B9" t="n">
-        <v>57415</v>
+        <v>57653</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,25 +1570,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102626</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1582,14 +1597,10 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1599,13 +1610,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441144</v>
+        <v>441187</v>
       </c>
       <c r="R9" t="n">
-        <v>6199119</v>
+        <v>6198844</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1634,7 +1645,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1653,7 +1664,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,7 +1682,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104226</v>
+        <v>120104234</v>
       </c>
       <c r="B10" t="n">
         <v>102241</v>
@@ -1723,10 +1734,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441085</v>
+        <v>441082</v>
       </c>
       <c r="R10" t="n">
-        <v>6198931</v>
+        <v>6198933</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1778,7 +1789,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1796,10 +1807,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105974</v>
+        <v>120105927</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>58023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,21 +1823,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1838,7 +1849,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1848,10 +1859,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441084</v>
+        <v>441110</v>
       </c>
       <c r="R11" t="n">
-        <v>6198915</v>
+        <v>6199010</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1889,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,7 +1908,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1915,10 +1926,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105396</v>
+        <v>120105974</v>
       </c>
       <c r="B12" t="n">
-        <v>57499</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1927,20 +1938,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1957,7 +1968,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1967,10 +1978,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441206</v>
+        <v>441084</v>
       </c>
       <c r="R12" t="n">
-        <v>6198969</v>
+        <v>6198915</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1997,12 +2008,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,7 +2027,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2034,10 +2045,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105410</v>
+        <v>120105570</v>
       </c>
       <c r="B13" t="n">
-        <v>57499</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,20 +2057,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2086,13 +2097,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441089</v>
+        <v>441194</v>
       </c>
       <c r="R13" t="n">
-        <v>6198892</v>
+        <v>6198838</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,12 +2127,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,7 +2146,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2153,10 +2164,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104234</v>
+        <v>120105410</v>
       </c>
       <c r="B14" t="n">
-        <v>102241</v>
+        <v>57499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,39 +2176,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225046</v>
+        <v>102623</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2205,13 +2216,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441082</v>
+        <v>441089</v>
       </c>
       <c r="R14" t="n">
-        <v>6198933</v>
+        <v>6198892</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2235,17 +2246,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,13 +2260,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2278,7 +2283,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103176</v>
+        <v>120103183</v>
       </c>
       <c r="B15" t="n">
         <v>99589</v>
@@ -2313,7 +2318,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2334,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441142</v>
+        <v>441109</v>
       </c>
       <c r="R15" t="n">
-        <v>6198980</v>
+        <v>6199104</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2402,10 +2407,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103183</v>
+        <v>120103243</v>
       </c>
       <c r="B16" t="n">
-        <v>99589</v>
+        <v>44696</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,54 +2419,63 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222617</v>
+        <v>100959</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441109</v>
+        <v>441208</v>
       </c>
       <c r="R16" t="n">
-        <v>6199104</v>
+        <v>6198925</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2488,12 +2502,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,7 +2527,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2526,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103243</v>
+        <v>120103176</v>
       </c>
       <c r="B17" t="n">
-        <v>44696</v>
+        <v>99589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2538,63 +2557,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100959</v>
+        <v>222617</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441208</v>
+        <v>441142</v>
       </c>
       <c r="R17" t="n">
-        <v>6198925</v>
+        <v>6198980</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2621,17 +2631,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,7 +2651,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2664,10 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120103099</v>
+        <v>120105396</v>
       </c>
       <c r="B18" t="n">
-        <v>106214</v>
+        <v>57499</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2676,43 +2681,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>102623</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2720,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441148</v>
+        <v>441206</v>
       </c>
       <c r="R18" t="n">
-        <v>6199058</v>
+        <v>6198969</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,12 +2751,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,13 +2765,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105904</v>
+        <v>120105410</v>
       </c>
       <c r="B2" t="n">
-        <v>57339</v>
+        <v>57499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>102623</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120102422</v>
+        <v>120102976</v>
       </c>
       <c r="B3" t="n">
-        <v>56276</v>
+        <v>106214</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,59 +806,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100070</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441168</v>
+        <v>441198</v>
       </c>
       <c r="R3" t="n">
-        <v>6198861</v>
+        <v>6198938</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,11 +888,6 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120104226</v>
+        <v>120105542</v>
       </c>
       <c r="B4" t="n">
-        <v>102241</v>
+        <v>57653</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,39 +930,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>225046</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,13 +970,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441085</v>
+        <v>441187</v>
       </c>
       <c r="R4" t="n">
-        <v>6198931</v>
+        <v>6198844</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,12 +1005,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Levande ung alm</t>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,13 +1019,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Lövrik tallskog, bryn</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120102976</v>
+        <v>120105904</v>
       </c>
       <c r="B5" t="n">
-        <v>106214</v>
+        <v>57339</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,43 +1054,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,13 +1094,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441198</v>
+        <v>441089</v>
       </c>
       <c r="R5" t="n">
-        <v>6198938</v>
+        <v>6198892</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,12 +1124,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,13 +1138,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103099</v>
+        <v>120105396</v>
       </c>
       <c r="B6" t="n">
-        <v>106214</v>
+        <v>57499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,43 +1173,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,13 +1213,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441148</v>
+        <v>441206</v>
       </c>
       <c r="R6" t="n">
-        <v>6199058</v>
+        <v>6198969</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,12 +1243,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,13 +1257,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102939</v>
+        <v>120104234</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>102241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,27 +1292,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1357,7 +1332,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441085</v>
+        <v>441082</v>
       </c>
       <c r="R7" t="n">
         <v>6198933</v>
@@ -1397,7 +1372,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Skogsholme, på höjd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1430,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105487</v>
+        <v>120103183</v>
       </c>
       <c r="B8" t="n">
-        <v>57415</v>
+        <v>99589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,43 +1417,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102626</v>
+        <v>222617</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1486,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441144</v>
+        <v>441109</v>
       </c>
       <c r="R8" t="n">
-        <v>6199119</v>
+        <v>6199104</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1516,17 +1491,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,12 +1505,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1558,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105542</v>
+        <v>120103243</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>44696</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,53 +1541,66 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>100959</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441187</v>
+        <v>441208</v>
       </c>
       <c r="R9" t="n">
-        <v>6198844</v>
+        <v>6198925</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,12 +1629,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,12 +1643,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1682,10 +1667,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104234</v>
+        <v>120105974</v>
       </c>
       <c r="B10" t="n">
-        <v>102241</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,39 +1679,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225046</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1734,13 +1719,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441082</v>
+        <v>441084</v>
       </c>
       <c r="R10" t="n">
-        <v>6198933</v>
+        <v>6198915</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1764,17 +1749,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,13 +1763,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1807,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120105927</v>
+        <v>120103099</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>106214</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,35 +1802,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1859,13 +1842,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441110</v>
+        <v>441148</v>
       </c>
       <c r="R11" t="n">
-        <v>6199010</v>
+        <v>6199058</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1903,12 +1886,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandslänt, hygge</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1926,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105974</v>
+        <v>120102422</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>56276</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,53 +1922,62 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100070</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441084</v>
+        <v>441168</v>
       </c>
       <c r="R12" t="n">
-        <v>6198915</v>
+        <v>6198861</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2008,12 +2001,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,12 +2020,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2045,10 +2044,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120105570</v>
+        <v>120102939</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2057,25 +2056,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2083,13 +2082,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2097,13 +2100,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441194</v>
+        <v>441085</v>
       </c>
       <c r="R13" t="n">
-        <v>6198838</v>
+        <v>6198933</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,18 +2138,24 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Skogsdunge, på höjd</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2164,10 +2173,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120105410</v>
+        <v>120103176</v>
       </c>
       <c r="B14" t="n">
-        <v>57499</v>
+        <v>99589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2176,39 +2185,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102623</v>
+        <v>222617</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2216,13 +2229,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441089</v>
+        <v>441142</v>
       </c>
       <c r="R14" t="n">
-        <v>6198892</v>
+        <v>6198980</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2260,12 +2273,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig vägslänt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2283,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103183</v>
+        <v>120104226</v>
       </c>
       <c r="B15" t="n">
-        <v>99589</v>
+        <v>102241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,40 +2309,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222617</v>
+        <v>225046</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2339,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441109</v>
+        <v>441085</v>
       </c>
       <c r="R15" t="n">
-        <v>6199104</v>
+        <v>6198931</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2369,12 +2379,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2389,7 +2404,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Skogsdunge, höjd</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2407,10 +2422,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103243</v>
+        <v>120105570</v>
       </c>
       <c r="B16" t="n">
-        <v>44696</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2419,66 +2434,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100959</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441208</v>
+        <v>441194</v>
       </c>
       <c r="R16" t="n">
-        <v>6198925</v>
+        <v>6198838</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2510,24 +2512,18 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Sandslänt</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103176</v>
+        <v>120105487</v>
       </c>
       <c r="B17" t="n">
-        <v>99589</v>
+        <v>57415</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,43 +2553,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222617</v>
+        <v>102626</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2601,13 +2597,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441142</v>
+        <v>441144</v>
       </c>
       <c r="R17" t="n">
-        <v>6198980</v>
+        <v>6199119</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2631,12 +2627,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,13 +2646,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120105396</v>
+        <v>120105927</v>
       </c>
       <c r="B18" t="n">
-        <v>57499</v>
+        <v>58023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102623</v>
+        <v>103055</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441206</v>
+        <v>441110</v>
       </c>
       <c r="R18" t="n">
-        <v>6198969</v>
+        <v>6199010</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105410</v>
+        <v>120102976</v>
       </c>
       <c r="B2" t="n">
-        <v>57499</v>
+        <v>106214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102623</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441089</v>
+        <v>441198</v>
       </c>
       <c r="R2" t="n">
-        <v>6198892</v>
+        <v>6198938</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,12 +775,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig slänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120102976</v>
+        <v>120105410</v>
       </c>
       <c r="B3" t="n">
-        <v>106214</v>
+        <v>57499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,43 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441198</v>
+        <v>441089</v>
       </c>
       <c r="R3" t="n">
-        <v>6198938</v>
+        <v>6198892</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,13 +895,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120104234</v>
+        <v>120104168</v>
       </c>
       <c r="B2" t="n">
-        <v>102241</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Helichrysum arenarium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441082</v>
+        <v>441055</v>
       </c>
       <c r="R2" t="n">
-        <v>6198933</v>
+        <v>6198897</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,11 +764,6 @@
           <t>2024-05-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsholme, på höjd</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120103243</v>
+        <v>120104173</v>
       </c>
       <c r="B3" t="n">
-        <v>44696</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,59 +805,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100959</v>
+        <v>762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckig myrlejonslända</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Euroleon nostras</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fourcroy, 1785)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441208</v>
+        <v>441061</v>
       </c>
       <c r="R3" t="n">
-        <v>6198925</v>
+        <v>6198897</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,11 +881,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,52 +913,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120103176</v>
+        <v>120104178</v>
       </c>
       <c r="B4" t="n">
-        <v>99589</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222617</v>
+        <v>762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -994,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441142</v>
+        <v>441065</v>
       </c>
       <c r="R4" t="n">
-        <v>6198980</v>
+        <v>6198889</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1014,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,52 +1032,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120102976</v>
+        <v>120104188</v>
       </c>
       <c r="B5" t="n">
-        <v>106214</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1118,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441198</v>
+        <v>441070</v>
       </c>
       <c r="R5" t="n">
-        <v>6198938</v>
+        <v>6198888</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1148,12 +1113,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1133,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sandig slänt</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102422</v>
+        <v>120104194</v>
       </c>
       <c r="B6" t="n">
-        <v>56276</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,55 +1162,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100070</v>
+        <v>762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441168</v>
+        <v>441061</v>
       </c>
       <c r="R6" t="n">
-        <v>6198861</v>
+        <v>6198895</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1277,17 +1232,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fjolårsunge. Låg under smärre träbit.</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1252,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Sandig vägkant</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,52 +1270,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103183</v>
+        <v>120104200</v>
       </c>
       <c r="B7" t="n">
-        <v>99589</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222617</v>
+        <v>762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1376,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441109</v>
+        <v>441070</v>
       </c>
       <c r="R7" t="n">
-        <v>6199104</v>
+        <v>6198884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1406,12 +1351,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,7 +1371,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandig vägslänt</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1444,15 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120105487</v>
+        <v>120105570</v>
       </c>
       <c r="B8" t="n">
-        <v>57415</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102626</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1483,11 +1423,7 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1500,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441144</v>
+        <v>441194</v>
       </c>
       <c r="R8" t="n">
-        <v>6199119</v>
+        <v>6198838</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1535,12 +1471,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppenbart revir.</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,7 +1485,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1572,37 +1503,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120105927</v>
+        <v>120105974</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1614,7 +1540,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1624,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441110</v>
+        <v>441084</v>
       </c>
       <c r="R9" t="n">
-        <v>6199010</v>
+        <v>6198915</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1654,12 +1580,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,7 +1599,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Skogsholme, äldre tallar</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1691,37 +1617,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120105570</v>
+        <v>120102281</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100070</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1729,27 +1650,44 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441194</v>
+        <v>441061</v>
       </c>
       <c r="R10" t="n">
-        <v>6198838</v>
+        <v>6198885</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,18 +1719,24 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Låg under smärre trädstam. Vårdräkt.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Sandig vägren, under klen trädstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,66 +1754,66 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103099</v>
+        <v>120102422</v>
       </c>
       <c r="B11" t="n">
-        <v>106214</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>100070</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441148</v>
+        <v>441168</v>
       </c>
       <c r="R11" t="n">
-        <v>6199058</v>
+        <v>6198861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1896,12 +1840,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårsunge. Låg under smärre träbit.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,7 +1865,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Sandslänt, hygge</t>
+          <t>Sandig vägkant</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1934,37 +1883,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120105396</v>
+        <v>120102721</v>
       </c>
       <c r="B12" t="n">
-        <v>57499</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102623</v>
+        <v>100070</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1972,27 +1916,40 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441206</v>
+        <v>441066</v>
       </c>
       <c r="R12" t="n">
-        <v>6198969</v>
+        <v>6198898</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2016,12 +1973,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I sandslänt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2030,12 +1992,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Nyupptaget hygge, efter tall</t>
+          <t>Sandig sydvänd slänt</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2053,66 +2016,70 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120102939</v>
+        <v>120102480</v>
       </c>
       <c r="B13" t="n">
-        <v>105588</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>100141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441085</v>
+        <v>441061</v>
       </c>
       <c r="R13" t="n">
-        <v>6198933</v>
+        <v>6198885</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2149,7 +2116,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En levande ung stam.</t>
+          <t>Låg under klen trädstam.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,7 +2131,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Skogsdunge, på höjd</t>
+          <t>Sandig vägren</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2182,65 +2149,73 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120105542</v>
+        <v>120103243</v>
       </c>
       <c r="B14" t="n">
-        <v>57653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103008</v>
+        <v>100959</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläckig myrlejonslända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Euroleon nostras</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fourcroy, 1785)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lyngsjö, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441187</v>
+        <v>441208</v>
       </c>
       <c r="R14" t="n">
-        <v>6198844</v>
+        <v>6198925</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2269,12 +2244,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppenbart revir.</t>
+          <t>Under grova rotben av tallstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,12 +2258,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Lövrik tallskog, bryn</t>
+          <t>Sandslänt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2306,32 +2282,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120105974</v>
+        <v>120105396</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2348,7 +2319,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2358,10 +2329,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441084</v>
+        <v>441206</v>
       </c>
       <c r="R15" t="n">
-        <v>6198915</v>
+        <v>6198969</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2388,12 +2359,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2407,7 +2378,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Skogsholme, äldre tallar</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2428,12 +2399,7 @@
         <v>120105410</v>
       </c>
       <c r="B16" t="n">
-        <v>57499</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,15 +2510,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120105904</v>
+        <v>120105487</v>
       </c>
       <c r="B17" t="n">
-        <v>57339</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2560,16 +2521,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>102626</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2583,10 +2544,14 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2596,10 +2561,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441089</v>
+        <v>441144</v>
       </c>
       <c r="R17" t="n">
-        <v>6198892</v>
+        <v>6199119</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2626,12 +2591,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,7 +2615,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Nyupptaget hygge, efter tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2663,51 +2633,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120104226</v>
+        <v>120105904</v>
       </c>
       <c r="B18" t="n">
-        <v>102241</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>225046</v>
+        <v>102977</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2715,13 +2680,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441085</v>
+        <v>441089</v>
       </c>
       <c r="R18" t="n">
-        <v>6198931</v>
+        <v>6198892</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2745,17 +2710,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Levande ung alm</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,13 +2724,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Skogsdunge, höjd</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2785,6 +2744,1793 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120105542</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>441187</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6198844</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Uppenbart revir.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Lövrik tallskog, bryn</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120105927</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>441110</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6199010</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Nyupptaget hygge, efter tall</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120102939</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>441085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6198933</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En levande ung stam.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Skogsdunge, på höjd</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120102976</v>
+      </c>
+      <c r="B22" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>441198</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6198938</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Sandig slänt</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120103009</v>
+      </c>
+      <c r="B23" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>441062</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6198897</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Sandslänt</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120103069</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>441063</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6198893</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Sandslänt</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120103085</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>441060</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6198894</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Sandslänt</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120103091</v>
+      </c>
+      <c r="B26" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>441063</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6198891</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Sandslänt</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120103099</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>441148</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6199058</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Sandslänt, hygge</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120103119</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>441061</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6198897</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Sandslänt</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120103176</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>441142</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6198980</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Sandig vägslänt</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120103183</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>441109</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6199104</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Sandig vägslänt</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120103200</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>441064</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6198902</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Sandig slänt</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120104226</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>441085</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6198931</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Skogsdunge, höjd</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120104234</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lyngsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>441082</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6198933</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lyngsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Levande ung alm</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Skogsholme, på höjd</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29875-2023 artfynd.xlsx
+++ b/artfynd/A 29875-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104178</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104194</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105570</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1614,6 +1654,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105974</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102281</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1880,6 +1930,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102422</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2013,6 +2068,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102721</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2146,6 +2206,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102480</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2279,6 +2344,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103243</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2393,6 +2463,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105396</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2507,6 +2582,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105410</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2630,6 +2710,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2744,6 +2829,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105904</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2863,6 +2953,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105542</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2977,6 +3072,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105927</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3101,6 +3201,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102939</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3220,6 +3325,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120102976</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3339,6 +3449,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103009</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3458,6 +3573,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3577,6 +3697,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103085</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3696,6 +3821,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103091</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3815,6 +3945,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103099</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3934,6 +4069,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103119</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4053,6 +4193,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103176</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4172,6 +4317,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103183</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4291,6 +4441,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120103200</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4411,6 +4566,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104226</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4531,8 +4691,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>